--- a/Team-Data/2014-15/1-30-2014-15.xlsx
+++ b/Team-Data/2014-15/1-30-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,25 +728,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" t="n">
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.83</v>
+        <v>0.826</v>
       </c>
       <c r="H2" t="n">
         <v>48.2</v>
       </c>
       <c r="I2" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J2" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0.473</v>
@@ -691,16 +758,16 @@
         <v>25.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.389</v>
+        <v>0.387</v>
       </c>
       <c r="O2" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P2" t="n">
         <v>22.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.773</v>
+        <v>0.776</v>
       </c>
       <c r="R2" t="n">
         <v>8.5</v>
@@ -718,43 +785,43 @@
         <v>14.3</v>
       </c>
       <c r="W2" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X2" t="n">
         <v>4.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AA2" t="n">
         <v>20.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.7</v>
+        <v>103.6</v>
       </c>
       <c r="AC2" t="n">
         <v>7.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ2" t="n">
         <v>27</v>
@@ -766,16 +833,16 @@
         <v>5</v>
       </c>
       <c r="AM2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN2" t="n">
         <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
         <v>8</v>
@@ -787,7 +854,7 @@
         <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -799,10 +866,10 @@
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" t="n">
         <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>0.356</v>
+        <v>0.364</v>
       </c>
       <c r="H3" t="n">
         <v>48.6</v>
       </c>
       <c r="I3" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="J3" t="n">
-        <v>87.8</v>
+        <v>87.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L3" t="n">
         <v>7.6</v>
@@ -873,31 +940,31 @@
         <v>23</v>
       </c>
       <c r="N3" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="O3" t="n">
         <v>14.9</v>
       </c>
       <c r="P3" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R3" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S3" t="n">
         <v>32.7</v>
       </c>
       <c r="T3" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U3" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="V3" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W3" t="n">
         <v>8</v>
@@ -915,7 +982,7 @@
         <v>18</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.4</v>
+        <v>101.8</v>
       </c>
       <c r="AC3" t="n">
         <v>-2</v>
@@ -924,16 +991,16 @@
         <v>28</v>
       </c>
       <c r="AE3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG3" t="n">
         <v>21</v>
       </c>
-      <c r="AG3" t="n">
-        <v>23</v>
-      </c>
       <c r="AH3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI3" t="n">
         <v>4</v>
@@ -942,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL3" t="n">
         <v>13</v>
@@ -957,16 +1024,16 @@
         <v>28</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>15</v>
@@ -978,7 +1045,7 @@
         <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX3" t="n">
         <v>25</v>
@@ -987,13 +1054,13 @@
         <v>23</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
         <v>18</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>0.391</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>36.3</v>
+        <v>36</v>
       </c>
       <c r="J4" t="n">
-        <v>81.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L4" t="n">
         <v>6.6</v>
@@ -1055,31 +1122,31 @@
         <v>20.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.316</v>
+        <v>0.318</v>
       </c>
       <c r="O4" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>32</v>
       </c>
       <c r="T4" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="U4" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="W4" t="n">
         <v>7.3</v>
@@ -1094,49 +1161,49 @@
         <v>20</v>
       </c>
       <c r="AA4" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC4" t="n">
         <v>-3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>20</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
         <v>20</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
         <v>19</v>
       </c>
       <c r="AL4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AM4" t="n">
         <v>18</v>
       </c>
       <c r="AN4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
         <v>21</v>
@@ -1148,16 +1215,16 @@
         <v>26</v>
       </c>
       <c r="AS4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV4" t="n">
         <v>16</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>15</v>
       </c>
       <c r="AW4" t="n">
         <v>19</v>
@@ -1169,10 +1236,10 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB4" t="n">
         <v>25</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1303,7 +1370,7 @@
         <v>27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK5" t="n">
         <v>29</v>
@@ -1321,7 +1388,7 @@
         <v>14</v>
       </c>
       <c r="AP5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>26</v>
@@ -1333,10 +1400,10 @@
         <v>9</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
@@ -1360,7 +1427,7 @@
         <v>27</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -1389,52 +1456,52 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>0.612</v>
+        <v>0.625</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J6" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>0.443</v>
       </c>
       <c r="L6" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M6" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.358</v>
+        <v>0.36</v>
       </c>
       <c r="O6" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="P6" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.782</v>
+        <v>0.785</v>
       </c>
       <c r="R6" t="n">
         <v>12.2</v>
       </c>
       <c r="S6" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="T6" t="n">
         <v>45.7</v>
@@ -1461,16 +1528,16 @@
         <v>22.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.1</v>
+        <v>102.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF6" t="n">
         <v>11</v>
@@ -1485,7 +1552,7 @@
         <v>20</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK6" t="n">
         <v>20</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1506,22 +1573,22 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR6" t="n">
         <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU6" t="n">
         <v>15</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
         <v>28</v>
@@ -1530,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1542,7 +1609,7 @@
         <v>9</v>
       </c>
       <c r="BC6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7" t="n">
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>0.583</v>
+        <v>0.574</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1592,34 +1659,34 @@
         <v>82.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="N7" t="n">
         <v>0.351</v>
       </c>
       <c r="O7" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P7" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.758</v>
+        <v>0.76</v>
       </c>
       <c r="R7" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S7" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="T7" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U7" t="n">
         <v>21.6</v>
@@ -1628,7 +1695,7 @@
         <v>13.6</v>
       </c>
       <c r="W7" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X7" t="n">
         <v>4</v>
@@ -1637,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
         <v>21.1</v>
@@ -1646,10 +1713,10 @@
         <v>101.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
@@ -1679,16 +1746,16 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>13</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>14</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
@@ -1697,7 +1764,7 @@
         <v>24</v>
       </c>
       <c r="AT7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU7" t="n">
         <v>13</v>
@@ -1706,13 +1773,13 @@
         <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
         <v>28</v>
       </c>
       <c r="AY7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ7" t="n">
         <v>1</v>
@@ -1721,7 +1788,7 @@
         <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -1756,34 +1823,34 @@
         <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>0.66</v>
+        <v>0.638</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="J8" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.469</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M8" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O8" t="n">
         <v>17</v>
@@ -1792,19 +1859,19 @@
         <v>22.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.761</v>
+        <v>0.766</v>
       </c>
       <c r="R8" t="n">
         <v>10.7</v>
       </c>
       <c r="S8" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T8" t="n">
-        <v>42.3</v>
+        <v>41.9</v>
       </c>
       <c r="U8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
         <v>12.4</v>
@@ -1819,28 +1886,28 @@
         <v>3.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB8" t="n">
-        <v>107</v>
+        <v>107.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
         <v>11</v>
@@ -1867,19 +1934,19 @@
         <v>19</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
         <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1888,7 +1955,7 @@
         <v>3</v>
       </c>
       <c r="AW8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
@@ -1897,7 +1964,7 @@
         <v>3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>3</v>
@@ -1906,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -2013,13 +2080,13 @@
         <v>-3</v>
       </c>
       <c r="AD9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG9" t="n">
         <v>19</v>
@@ -2046,7 +2113,7 @@
         <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
         <v>6</v>
@@ -2064,16 +2131,16 @@
         <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
         <v>27</v>
@@ -2088,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2204,16 +2271,16 @@
         <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
         <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
         <v>28</v>
@@ -2225,7 +2292,7 @@
         <v>7</v>
       </c>
       <c r="AN10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>23</v>
@@ -2240,13 +2307,13 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
@@ -2255,7 +2322,7 @@
         <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
         <v>16</v>
@@ -2267,7 +2334,7 @@
         <v>23</v>
       </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC10" t="n">
         <v>19</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" t="n">
         <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.837</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="J11" t="n">
         <v>86.7</v>
       </c>
       <c r="K11" t="n">
-        <v>0.483</v>
+        <v>0.484</v>
       </c>
       <c r="L11" t="n">
         <v>10.3</v>
@@ -2329,37 +2396,37 @@
         <v>26.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0.384</v>
+        <v>0.387</v>
       </c>
       <c r="O11" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P11" t="n">
         <v>21.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.776</v>
+        <v>0.778</v>
       </c>
       <c r="R11" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S11" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="T11" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="U11" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W11" t="n">
         <v>9.4</v>
       </c>
       <c r="X11" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Y11" t="n">
         <v>3.6</v>
@@ -2371,10 +2438,10 @@
         <v>19</v>
       </c>
       <c r="AB11" t="n">
-        <v>110.9</v>
+        <v>111.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD11" t="n">
         <v>30</v>
@@ -2386,7 +2453,7 @@
         <v>1</v>
       </c>
       <c r="AG11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
@@ -2416,13 +2483,13 @@
         <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR11" t="n">
         <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -2431,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW11" t="n">
         <v>4</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -2496,46 +2563,46 @@
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J12" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K12" t="n">
         <v>0.44</v>
       </c>
       <c r="L12" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="M12" t="n">
         <v>33.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="O12" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="P12" t="n">
-        <v>24.1</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.722</v>
+        <v>0.719</v>
       </c>
       <c r="R12" t="n">
         <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T12" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U12" t="n">
         <v>21.2</v>
       </c>
       <c r="V12" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="W12" t="n">
         <v>9.9</v>
@@ -2544,22 +2611,22 @@
         <v>4.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.6</v>
+        <v>102.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2571,16 +2638,16 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK12" t="n">
         <v>21</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>22</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2589,22 +2656,22 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT12" t="n">
         <v>13</v>
@@ -2619,19 +2686,19 @@
         <v>1</v>
       </c>
       <c r="AX12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA12" t="n">
         <v>14</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -2750,16 +2817,16 @@
         <v>25</v>
       </c>
       <c r="AG13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH13" t="n">
         <v>18</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
@@ -2783,7 +2850,7 @@
         <v>16</v>
       </c>
       <c r="AR13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
@@ -2792,7 +2859,7 @@
         <v>6</v>
       </c>
       <c r="AU13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV13" t="n">
         <v>18</v>
@@ -2801,7 +2868,7 @@
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY13" t="n">
         <v>17</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -2845,43 +2912,43 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" t="n">
         <v>32</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.681</v>
+        <v>0.696</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J14" t="n">
-        <v>82.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474</v>
+        <v>0.475</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="M14" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.38</v>
+        <v>0.383</v>
       </c>
       <c r="O14" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P14" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q14" t="n">
         <v>0.747</v>
@@ -2893,19 +2960,19 @@
         <v>32.2</v>
       </c>
       <c r="T14" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U14" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="V14" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="W14" t="n">
         <v>7.7</v>
       </c>
       <c r="X14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="n">
         <v>3</v>
@@ -2914,25 +2981,25 @@
         <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.9</v>
+        <v>107</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2941,7 +3008,7 @@
         <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
@@ -2962,7 +3029,7 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR14" t="n">
         <v>27</v>
@@ -2992,7 +3059,7 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E15" t="n">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>0.283</v>
+        <v>0.277</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M15" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N15" t="n">
         <v>0.346</v>
       </c>
       <c r="O15" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="P15" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.745</v>
+        <v>0.747</v>
       </c>
       <c r="R15" t="n">
         <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T15" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U15" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V15" t="n">
         <v>13.1</v>
@@ -3093,19 +3160,19 @@
         <v>4.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.3</v>
+        <v>-6.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,10 +3184,10 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ15" t="n">
         <v>8</v>
@@ -3129,16 +3196,16 @@
         <v>24</v>
       </c>
       <c r="AL15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM15" t="n">
         <v>23</v>
       </c>
-      <c r="AM15" t="n">
-        <v>22</v>
-      </c>
       <c r="AN15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP15" t="n">
         <v>8</v>
@@ -3153,31 +3220,31 @@
         <v>18</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
         <v>7</v>
       </c>
       <c r="AW15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY15" t="n">
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>5.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3302,13 +3369,13 @@
         <v>1</v>
       </c>
       <c r="AI16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK16" t="n">
         <v>8</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>28</v>
@@ -3317,16 +3384,16 @@
         <v>27</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO16" t="n">
         <v>7</v>
       </c>
       <c r="AP16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
         <v>22</v>
@@ -3341,7 +3408,7 @@
         <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW16" t="n">
         <v>8</v>
@@ -3359,7 +3426,7 @@
         <v>11</v>
       </c>
       <c r="BB16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -3391,85 +3458,85 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" t="n">
         <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>0.435</v>
+        <v>0.444</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="J17" t="n">
-        <v>74.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.455</v>
+        <v>0.459</v>
       </c>
       <c r="L17" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M17" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="O17" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P17" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="R17" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="T17" t="n">
-        <v>37.7</v>
+        <v>37.3</v>
       </c>
       <c r="U17" t="n">
         <v>19.9</v>
       </c>
       <c r="V17" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X17" t="n">
         <v>4.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>92.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.7</v>
+        <v>-3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,25 +3557,25 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
       </c>
       <c r="AM17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
         <v>11</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3523,10 +3590,10 @@
         <v>29</v>
       </c>
       <c r="AV17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX17" t="n">
         <v>26</v>
@@ -3538,10 +3605,10 @@
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC17" t="n">
         <v>24</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>1.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
@@ -3669,10 +3736,10 @@
         <v>13</v>
       </c>
       <c r="AJ18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL18" t="n">
         <v>18</v>
@@ -3714,7 +3781,7 @@
         <v>14</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" t="n">
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>0.174</v>
+        <v>0.178</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J19" t="n">
-        <v>84.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>0.435</v>
@@ -3788,58 +3855,58 @@
         <v>0.335</v>
       </c>
       <c r="O19" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P19" t="n">
         <v>24.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.75</v>
+        <v>0.748</v>
       </c>
       <c r="R19" t="n">
         <v>12.1</v>
       </c>
       <c r="S19" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="T19" t="n">
         <v>41</v>
       </c>
       <c r="U19" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V19" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W19" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X19" t="n">
         <v>4.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z19" t="n">
         <v>19.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC19" t="n">
         <v>-9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
       </c>
       <c r="AF19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG19" t="n">
         <v>30</v>
@@ -3851,7 +3918,7 @@
         <v>19</v>
       </c>
       <c r="AJ19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -3866,13 +3933,13 @@
         <v>22</v>
       </c>
       <c r="AO19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP19" t="n">
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR19" t="n">
         <v>4</v>
@@ -3881,13 +3948,13 @@
         <v>30</v>
       </c>
       <c r="AT19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU19" t="n">
         <v>11</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW19" t="n">
         <v>7</v>
@@ -3899,13 +3966,13 @@
         <v>28</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
         <v>7</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC19" t="n">
         <v>29</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -3952,70 +4019,70 @@
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J20" t="n">
-        <v>83.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="M20" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.348</v>
+        <v>0.341</v>
       </c>
       <c r="O20" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.766</v>
+        <v>0.755</v>
       </c>
       <c r="R20" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="S20" t="n">
         <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="U20" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V20" t="n">
         <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="X20" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
         <v>19.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
@@ -4027,61 +4094,61 @@
         <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS20" t="n">
         <v>16</v>
       </c>
-      <c r="AO20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>17</v>
-      </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV20" t="n">
         <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY20" t="n">
         <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -4197,13 +4264,13 @@
         <v>-7.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG21" t="n">
         <v>29</v>
@@ -4224,10 +4291,10 @@
         <v>15</v>
       </c>
       <c r="AM21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4239,7 +4306,7 @@
         <v>11</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>28</v>
@@ -4254,7 +4321,7 @@
         <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX21" t="n">
         <v>27</v>
@@ -4266,10 +4333,10 @@
         <v>25</v>
       </c>
       <c r="BA21" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB21" t="n">
         <v>29</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>28</v>
       </c>
       <c r="BC21" t="n">
         <v>28</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>1</v>
       </c>
       <c r="AD22" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>16</v>
@@ -4391,16 +4458,16 @@
         <v>16</v>
       </c>
       <c r="AH22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI22" t="n">
         <v>15</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>16</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
         <v>16</v>
@@ -4409,16 +4476,16 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP22" t="n">
         <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR22" t="n">
         <v>5</v>
@@ -4430,10 +4497,10 @@
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
         <v>18</v>
@@ -4442,7 +4509,7 @@
         <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
         <v>28</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E23" t="n">
         <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
-        <v>0.313</v>
+        <v>0.306</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J23" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N23" t="n">
         <v>0.362</v>
@@ -4522,16 +4589,16 @@
         <v>19.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="R23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>40.3</v>
+        <v>40.6</v>
       </c>
       <c r="U23" t="n">
         <v>20.3</v>
@@ -4540,28 +4607,28 @@
         <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA23" t="n">
         <v>18.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.09999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.9</v>
+        <v>-6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4573,22 +4640,22 @@
         <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI23" t="n">
         <v>17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
         <v>20</v>
       </c>
       <c r="AM23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN23" t="n">
         <v>8</v>
@@ -4597,7 +4664,7 @@
         <v>29</v>
       </c>
       <c r="AP23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ23" t="n">
         <v>27</v>
@@ -4612,25 +4679,25 @@
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX23" t="n">
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>21</v>
       </c>
       <c r="BA23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F24" t="n">
         <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>0.213</v>
+        <v>0.196</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="J24" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.41</v>
+        <v>0.408</v>
       </c>
       <c r="L24" t="n">
         <v>7</v>
@@ -4695,55 +4762,55 @@
         <v>23.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0.298</v>
+        <v>0.297</v>
       </c>
       <c r="O24" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P24" t="n">
         <v>24.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="R24" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S24" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T24" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="U24" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="V24" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="W24" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Y24" t="n">
         <v>5.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>89.7</v>
+        <v>89.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>-11.6</v>
+        <v>-12.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4776,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4791,10 +4858,10 @@
         <v>27</v>
       </c>
       <c r="AT24" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4806,13 +4873,13 @@
         <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -4847,61 +4914,61 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F25" t="n">
         <v>20</v>
       </c>
       <c r="G25" t="n">
-        <v>0.583</v>
+        <v>0.574</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="J25" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>0.466</v>
       </c>
       <c r="L25" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O25" t="n">
         <v>17.2</v>
       </c>
       <c r="P25" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.791</v>
+        <v>0.789</v>
       </c>
       <c r="R25" t="n">
         <v>10.5</v>
       </c>
       <c r="S25" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="T25" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U25" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V25" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W25" t="n">
         <v>8.699999999999999</v>
@@ -4916,16 +4983,16 @@
         <v>22.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>107.2</v>
+        <v>107.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
@@ -4937,7 +5004,7 @@
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI25" t="n">
         <v>3</v>
@@ -4946,7 +5013,7 @@
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL25" t="n">
         <v>6</v>
@@ -4958,7 +5025,7 @@
         <v>9</v>
       </c>
       <c r="AO25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
@@ -4976,7 +5043,7 @@
         <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV25" t="n">
         <v>23</v>
@@ -4985,13 +5052,13 @@
         <v>6</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA25" t="n">
         <v>13</v>
@@ -5000,7 +5067,7 @@
         <v>2</v>
       </c>
       <c r="BC25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E26" t="n">
         <v>32</v>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>0.681</v>
+        <v>0.696</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
@@ -5056,40 +5123,40 @@
         <v>10.2</v>
       </c>
       <c r="M26" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="N26" t="n">
         <v>0.37</v>
       </c>
       <c r="O26" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P26" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.794</v>
+        <v>0.793</v>
       </c>
       <c r="R26" t="n">
         <v>10.9</v>
       </c>
       <c r="S26" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="T26" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="U26" t="n">
         <v>22.4</v>
       </c>
       <c r="V26" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W26" t="n">
         <v>6.8</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y26" t="n">
         <v>3.5</v>
@@ -5098,28 +5165,28 @@
         <v>19.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>4</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
         <v>9</v>
@@ -5149,10 +5216,10 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT26" t="n">
         <v>4</v>
@@ -5164,7 +5231,7 @@
         <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
         <v>9</v>
@@ -5173,16 +5240,16 @@
         <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA26" t="n">
         <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -5211,37 +5278,37 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" t="n">
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G27" t="n">
-        <v>0.356</v>
+        <v>0.364</v>
       </c>
       <c r="H27" t="n">
         <v>48.7</v>
       </c>
       <c r="I27" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J27" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.455</v>
+        <v>0.457</v>
       </c>
       <c r="L27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="M27" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0.33</v>
+        <v>0.334</v>
       </c>
       <c r="O27" t="n">
         <v>23.2</v>
@@ -5250,19 +5317,19 @@
         <v>29.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R27" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S27" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T27" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U27" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V27" t="n">
         <v>16.5</v>
@@ -5277,40 +5344,40 @@
         <v>6.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA27" t="n">
         <v>24.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.4</v>
+        <v>101.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-3.1</v>
+        <v>-2.9</v>
       </c>
       <c r="AD27" t="n">
         <v>28</v>
       </c>
       <c r="AE27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG27" t="n">
         <v>21</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>23</v>
       </c>
       <c r="AH27" t="n">
         <v>5</v>
       </c>
       <c r="AI27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5361,10 +5428,10 @@
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F28" t="n">
         <v>17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.63</v>
+        <v>0.638</v>
       </c>
       <c r="H28" t="n">
         <v>49</v>
@@ -5411,25 +5478,25 @@
         <v>38</v>
       </c>
       <c r="J28" t="n">
-        <v>83.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0.365</v>
+        <v>0.368</v>
       </c>
       <c r="O28" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P28" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="Q28" t="n">
         <v>0.768</v>
@@ -5438,19 +5505,19 @@
         <v>10</v>
       </c>
       <c r="S28" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T28" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W28" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X28" t="n">
         <v>5.5</v>
@@ -5462,34 +5529,34 @@
         <v>19.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB28" t="n">
         <v>101.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="AE28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
         <v>12</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>12</v>
@@ -5504,10 +5571,10 @@
         <v>7</v>
       </c>
       <c r="AO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
         <v>10</v>
@@ -5519,16 +5586,16 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
@@ -5540,7 +5607,7 @@
         <v>10</v>
       </c>
       <c r="BA28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB28" t="n">
         <v>14</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -5575,52 +5642,52 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F29" t="n">
         <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>0.681</v>
+        <v>0.674</v>
       </c>
       <c r="H29" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>38.9</v>
+        <v>38.7</v>
       </c>
       <c r="J29" t="n">
-        <v>84.7</v>
+        <v>84.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L29" t="n">
         <v>8.9</v>
       </c>
       <c r="M29" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="O29" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P29" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.783</v>
+        <v>0.78</v>
       </c>
       <c r="R29" t="n">
         <v>11.4</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T29" t="n">
         <v>42</v>
@@ -5629,7 +5696,7 @@
         <v>21.1</v>
       </c>
       <c r="V29" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="W29" t="n">
         <v>7.5</v>
@@ -5647,34 +5714,34 @@
         <v>21.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="AC29" t="n">
         <v>5.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AI29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ29" t="n">
         <v>12</v>
       </c>
       <c r="AK29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5692,7 +5759,7 @@
         <v>3</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR29" t="n">
         <v>11</v>
@@ -5701,19 +5768,19 @@
         <v>26</v>
       </c>
       <c r="AT29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -5757,25 +5824,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F30" t="n">
         <v>30</v>
       </c>
       <c r="G30" t="n">
-        <v>0.362</v>
+        <v>0.348</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J30" t="n">
-        <v>79.3</v>
+        <v>79</v>
       </c>
       <c r="K30" t="n">
         <v>0.451</v>
@@ -5787,34 +5854,34 @@
         <v>21.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O30" t="n">
         <v>17.1</v>
       </c>
       <c r="P30" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.745</v>
+        <v>0.749</v>
       </c>
       <c r="R30" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S30" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="T30" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U30" t="n">
         <v>20.3</v>
       </c>
       <c r="V30" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W30" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X30" t="n">
         <v>5.9</v>
@@ -5823,28 +5890,28 @@
         <v>4.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA30" t="n">
         <v>19.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>95.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-2.6</v>
+        <v>-2.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF30" t="n">
         <v>23</v>
       </c>
       <c r="AG30" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5856,7 +5923,7 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="n">
         <v>17</v>
@@ -5865,19 +5932,19 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ30" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5886,7 +5953,7 @@
         <v>17</v>
       </c>
       <c r="AU30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV30" t="n">
         <v>26</v>
@@ -5910,7 +5977,7 @@
         <v>24</v>
       </c>
       <c r="BC30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
@@ -6017,10 +6084,10 @@
         <v>2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF31" t="n">
         <v>8</v>
@@ -6035,7 +6102,7 @@
         <v>6</v>
       </c>
       <c r="AJ31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK31" t="n">
         <v>3</v>
@@ -6062,7 +6129,7 @@
         <v>21</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
@@ -6074,7 +6141,7 @@
         <v>20</v>
       </c>
       <c r="AW31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX31" t="n">
         <v>13</v>
@@ -6086,10 +6153,10 @@
         <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC31" t="n">
         <v>12</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-30-2014-15</t>
+          <t>2015-01-30</t>
         </is>
       </c>
     </row>
